--- a/artfynd/A 21911-2026 artfynd.xlsx
+++ b/artfynd/A 21911-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111412870</v>
+        <v>111413026</v>
       </c>
       <c r="B2" t="n">
-        <v>108022</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219677</v>
+        <v>1068</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Liten stinksvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Mutinus caninus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.:Pers.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493001.1390786725</v>
+        <v>492829</v>
       </c>
       <c r="R2" t="n">
-        <v>6227751.92766118</v>
+        <v>6227997</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,19 +746,9 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111413026</v>
+        <v>111412885</v>
       </c>
       <c r="B3" t="n">
-        <v>89007</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93082</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1068</v>
+        <v>1428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten stinksvamp</t>
+          <t>Rutkremla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mutinus caninus</t>
+          <t>Russula virescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.:Pers.) Fr.</t>
+          <t>(Schaeff.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492828.1855948549</v>
+        <v>493001</v>
       </c>
       <c r="R3" t="n">
-        <v>6227996.970613244</v>
+        <v>6227752</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -868,19 +847,9 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111412858</v>
+        <v>111413114</v>
       </c>
       <c r="B4" t="n">
-        <v>103369</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,27 +888,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221423</v>
+        <v>2979</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Lömsk flugsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Amanita phalloides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Fr.:Fr.) Link</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493001.1390786725</v>
+        <v>492814</v>
       </c>
       <c r="R4" t="n">
-        <v>6227751.92766118</v>
+        <v>6227924</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -985,19 +948,9 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111412863</v>
+        <v>111412870</v>
       </c>
       <c r="B5" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493001.1390786725</v>
+        <v>493001</v>
       </c>
       <c r="R5" t="n">
-        <v>6227751.92766118</v>
+        <v>6227752</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1102,19 +1050,9 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,15 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111413114</v>
+        <v>111412858</v>
       </c>
       <c r="B6" t="n">
-        <v>84776</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,26 +1091,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2979</v>
+        <v>221423</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lömsk flugsvamp</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Amanita phalloides</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Link</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492814.1280156323</v>
+        <v>493001</v>
       </c>
       <c r="R6" t="n">
-        <v>6227924.124954971</v>
+        <v>6227752</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1218,19 +1152,9 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,15 +1182,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111412885</v>
+        <v>111412863</v>
       </c>
       <c r="B7" t="n">
-        <v>90536</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,26 +1193,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1428</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rutkremla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Russula virescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1301,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493001.1390786725</v>
+        <v>493001</v>
       </c>
       <c r="R7" t="n">
-        <v>6227751.92766118</v>
+        <v>6227752</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1334,19 +1254,9 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 21911-2026 artfynd.xlsx
+++ b/artfynd/A 21911-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111413026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111412885</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111413114</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111412870</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111412858</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,8 +1311,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111412863</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>